--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,495 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129683825</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78829</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kolarsjön, Kolarsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>498301</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6853427</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129683973</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78829</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>498300</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6853687</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129682510</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79166</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>967</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kolarsjön, Kolarsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>498462</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6853325</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129682214</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56924</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>498331</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6853741</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129683920</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78829</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>498320</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6853529</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129683825</v>
       </c>
       <c r="B3" t="n">
-        <v>78829</v>
+        <v>78833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129683973</v>
       </c>
       <c r="B4" t="n">
-        <v>78829</v>
+        <v>78833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129682510</v>
       </c>
       <c r="B5" t="n">
-        <v>79166</v>
+        <v>79170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129682214</v>
       </c>
       <c r="B6" t="n">
-        <v>56924</v>
+        <v>56928</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>129683920</v>
       </c>
       <c r="B7" t="n">
-        <v>78829</v>
+        <v>78833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129683825</v>
       </c>
       <c r="B3" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129683973</v>
+        <v>129682510</v>
       </c>
       <c r="B4" t="n">
-        <v>78833</v>
+        <v>79171</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,34 +892,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+          <t>Kolarsjön, Kolarsjön, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498300</v>
+        <v>498462</v>
       </c>
       <c r="R4" t="n">
-        <v>6853687</v>
+        <v>6853325</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129682510</v>
+        <v>129683973</v>
       </c>
       <c r="B5" t="n">
-        <v>79170</v>
+        <v>78834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kolarsjön, Kolarsjön, Hls</t>
+          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498462</v>
+        <v>498300</v>
       </c>
       <c r="R5" t="n">
-        <v>6853325</v>
+        <v>6853687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1078,7 @@
         <v>129682214</v>
       </c>
       <c r="B6" t="n">
-        <v>56928</v>
+        <v>56929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>129683920</v>
       </c>
       <c r="B7" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129683825</v>
       </c>
       <c r="B3" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129682510</v>
+        <v>129683973</v>
       </c>
       <c r="B4" t="n">
-        <v>79171</v>
+        <v>78839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,34 +892,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kolarsjön, Kolarsjön, Hls</t>
+          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498462</v>
+        <v>498300</v>
       </c>
       <c r="R4" t="n">
-        <v>6853325</v>
+        <v>6853687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129683973</v>
+        <v>129682510</v>
       </c>
       <c r="B5" t="n">
-        <v>78834</v>
+        <v>79176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+          <t>Kolarsjön, Kolarsjön, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498300</v>
+        <v>498462</v>
       </c>
       <c r="R5" t="n">
-        <v>6853687</v>
+        <v>6853325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>129683920</v>
       </c>
       <c r="B7" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129683973</v>
+        <v>129682510</v>
       </c>
       <c r="B4" t="n">
-        <v>78839</v>
+        <v>79176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,34 +892,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+          <t>Kolarsjön, Kolarsjön, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498300</v>
+        <v>498462</v>
       </c>
       <c r="R4" t="n">
-        <v>6853687</v>
+        <v>6853325</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129682510</v>
+        <v>129683973</v>
       </c>
       <c r="B5" t="n">
-        <v>79176</v>
+        <v>78839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kolarsjön, Kolarsjön, Hls</t>
+          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498462</v>
+        <v>498300</v>
       </c>
       <c r="R5" t="n">
-        <v>6853325</v>
+        <v>6853687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129682510</v>
+        <v>129683973</v>
       </c>
       <c r="B4" t="n">
-        <v>79176</v>
+        <v>78839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,34 +892,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kolarsjön, Kolarsjön, Hls</t>
+          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498462</v>
+        <v>498300</v>
       </c>
       <c r="R4" t="n">
-        <v>6853325</v>
+        <v>6853687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129683973</v>
+        <v>129682510</v>
       </c>
       <c r="B5" t="n">
-        <v>78839</v>
+        <v>79176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+          <t>Kolarsjön, Kolarsjön, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498300</v>
+        <v>498462</v>
       </c>
       <c r="R5" t="n">
-        <v>6853687</v>
+        <v>6853325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129683825</v>
       </c>
       <c r="B3" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129683973</v>
+        <v>129682510</v>
       </c>
       <c r="B4" t="n">
-        <v>78839</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,34 +892,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+          <t>Kolarsjön, Kolarsjön, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498300</v>
+        <v>498462</v>
       </c>
       <c r="R4" t="n">
-        <v>6853687</v>
+        <v>6853325</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129682510</v>
+        <v>129683973</v>
       </c>
       <c r="B5" t="n">
-        <v>79176</v>
+        <v>78842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kolarsjön, Kolarsjön, Hls</t>
+          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498462</v>
+        <v>498300</v>
       </c>
       <c r="R5" t="n">
-        <v>6853325</v>
+        <v>6853687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1078,7 @@
         <v>129682214</v>
       </c>
       <c r="B6" t="n">
-        <v>56929</v>
+        <v>56930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>129683920</v>
       </c>
       <c r="B7" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129683825</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129682510</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129683973</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129682214</v>
       </c>
       <c r="B6" t="n">
-        <v>56930</v>
+        <v>56933</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>129683920</v>
       </c>
       <c r="B7" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129682510</v>
+        <v>129683973</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>78845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,34 +892,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kolarsjön, Kolarsjön, Hls</t>
+          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498462</v>
+        <v>498300</v>
       </c>
       <c r="R4" t="n">
-        <v>6853325</v>
+        <v>6853687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129683973</v>
+        <v>129682510</v>
       </c>
       <c r="B5" t="n">
-        <v>78845</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+          <t>Kolarsjön, Kolarsjön, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498300</v>
+        <v>498462</v>
       </c>
       <c r="R5" t="n">
-        <v>6853687</v>
+        <v>6853325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129683825</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129683973</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129682510</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>129683920</v>
       </c>
       <c r="B7" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129683825</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129683973</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129682510</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>129683920</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78882546</v>
+        <v>129682510</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Torpberget, Hls</t>
+          <t>Kolarsjön, Kolarsjön, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498480.8382813197</v>
+        <v>498462</v>
       </c>
       <c r="R2" t="n">
-        <v>6853647.293985726</v>
+        <v>6853325</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,67 +754,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129683825</v>
+        <v>78882544</v>
       </c>
       <c r="B3" t="n">
-        <v>78847</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolarsjön, Kolarsjön, Hls</t>
+          <t>Torpberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498301</v>
+        <v>498454</v>
       </c>
       <c r="R3" t="n">
-        <v>6853427</v>
+        <v>6853666</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,60 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129682510</v>
+        <v>78882545</v>
       </c>
       <c r="B4" t="n">
-        <v>79184</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kolarsjön, Kolarsjön, Hls</t>
+          <t>Torpberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498462</v>
+        <v>498474</v>
       </c>
       <c r="R4" t="n">
-        <v>6853325</v>
+        <v>6853644</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -946,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,57 +954,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129683973</v>
+        <v>129683495</v>
       </c>
       <c r="B5" t="n">
-        <v>78847</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+          <t>Kolarsjön, Kolarsjön, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498300</v>
+        <v>498263</v>
       </c>
       <c r="R5" t="n">
-        <v>6853687</v>
+        <v>6853400</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1066,7 @@
         <v>129682214</v>
       </c>
       <c r="B6" t="n">
-        <v>56933</v>
+        <v>57144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,48 +1164,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129683920</v>
+        <v>78882546</v>
       </c>
       <c r="B7" t="n">
-        <v>78847</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+          <t>Torpberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498320</v>
+        <v>498481</v>
       </c>
       <c r="R7" t="n">
-        <v>6853529</v>
+        <v>6853647</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1241,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1255,21 +1239,313 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129683825</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kolarsjön, Kolarsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>498301</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6853427</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129683920</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>498320</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6853529</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129683973</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kängalammsbäcken, Kängalammsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>498300</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6853687</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53654-2025 artfynd.xlsx
+++ b/artfynd/A 53654-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129682510</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78882544</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78882545</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129683495</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129682214</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78882546</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129683825</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129683920</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,8 +1591,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129683973</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>